--- a/data/Buff.xlsx
+++ b/data/Buff.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF25"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,9 +533,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
@@ -2563,6 +2560,477 @@
       </c>
       <c r="AF25" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>11103</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>赤甲镇关·防御提升(职业技能,幅度见 Skill.buff_percent)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ClassSkillBuff</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>12</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>11104</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>戈鸣断势·物伤降低(职业技能,幅度见 Skill.buff_percent)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ClassSkillBuff</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>11203</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>寒星凝魄·速度降低(职业技能,幅度见 Skill.buff_percent)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ClassSkillBuff</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>12</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>11304</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>灵鼎护元·防御提升(职业技能,幅度见 Skill.buff_percent)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ClassSkillBuff</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>12</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11403</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>青羽催行·速度提升(职业技能,幅度见 Skill.buff_percent)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ClassSkillBuff</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>11404</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>缚岚止步·速度降低(职业技能,幅度见 Skill.buff_percent)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ClassSkillBuff</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
